--- a/PR_PopulationSize_LowRep.xlsx
+++ b/PR_PopulationSize_LowRep.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,49 +549,49 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.99</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="I2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.9</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.89</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="N2" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="P2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -643,106 +643,104 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
+      <c r="B3" t="n">
+        <v>0.01</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="N3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.64</v>
+        <v>0.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -750,62 +748,62 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.01</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
@@ -847,110 +845,6 @@
       </c>
       <c r="AH4" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.86</v>
       </c>
     </row>
   </sheetData>
